--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -20,13 +20,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="0078350f"/>
+      <sz val="17"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001a2744"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -42,30 +59,32 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <color rgb="0078350f"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="0078350f"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +101,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="001a2744"/>
         <bgColor rgb="001a2744"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fee2e2"/>
+        <bgColor rgb="00fee2e2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d1fae5"/>
+        <bgColor rgb="00d1fae5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00dbeafe"/>
+        <bgColor rgb="00dbeafe"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fce7f3"/>
+        <bgColor rgb="00fce7f3"/>
       </patternFill>
     </fill>
     <fill>
@@ -117,27 +160,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -505,14 +566,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="44" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>봉이모바일 공통폼 템플릿 — 오프라인</t>
@@ -555,23 +616,23 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4. 값 단위: 만원 · 음수 = 페이백(고객 수령) · 양수 = 고객 부담</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>🔑 유심 정책 (핵심)</t>
+          <t>4. 값 단위: 만원 · 음수=페이백(고객 수령, 초록) · 양수=고객 부담(빨강)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>5. 인터넷/인터넷+TV 컬럼 = 결합 가입 시 추가 혜택 (전 행 공통)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>· 유심 변경 = 기기 그대로 · 유심만 다른 통신사로 교체</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>📊 포함 데이터 (정리3 원본)</t>
         </is>
       </c>
     </row>
@@ -579,7 +640,7 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· MNP(번호이동)만 가능 · 010 신규 제외</t>
+          <t>· 무선(휴대폰): 3사 × 18종 = 54행 (SK 프리미엄 / KT 초이스스페셜 / LG 프리미어 슈퍼)</t>
         </is>
       </c>
     </row>
@@ -587,7 +648,7 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>· 선택약정 기반 월 요금 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
+          <t>· 유심: 오프라인 5행 / 온라인 8행 (본 파일은 오프라인)</t>
         </is>
       </c>
     </row>
@@ -595,23 +656,23 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품에서 차감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
+          <t>· 인터넷+TV 사은품: 현금 1종 (금액은 매장/온라인 지정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>🔑 유심 정책 (핵심)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ 주의</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>· 유심 변경 = 기기 그대로 · 유심만 다른 통신사로 교체</t>
         </is>
       </c>
     </row>
@@ -619,7 +680,7 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>· 이 파일은 "오프라인" 전용 — 다른 채널과 섞지 말 것</t>
+          <t>· MNP(번호이동)만 가능 · 010 신규 제외</t>
         </is>
       </c>
     </row>
@@ -627,7 +688,63 @@
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>· 오프라인은 매장별 별도 파일 (총 12개) · 온라인은 통합 1개</t>
+          <t>· 선택약정 기반 월 요금 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품에서 차감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>· 개통: 유심 수령 후 고객센터 수령 통화 → 개통 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>· 이 파일은 "오프라인" 전용 — 다른 채널과 섞지 말 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>· 오프라인: 12개 매장 각자 복사해서 사용 (지역/협상력 반영)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>· 온라인: 통합 1개 파일 (전국 동일 가격)</t>
         </is>
       </c>
     </row>
@@ -645,25 +762,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📱 무선(휴대폰) 시세 — 오프라인</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+          <t>📱 무선(휴대폰) 시세 — 오프라인 · 3사 × 18종 = 54행</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>통신사</t>
@@ -681,7 +800,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>요금제(월요금)</t>
+          <t>요금제</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -692,6 +811,16 @@
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>기변</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>인터넷</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>인터넷+TV</t>
         </is>
       </c>
     </row>
@@ -701,82 +830,100 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>SM-S948N</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>S26U</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>프리미엄(125,000)</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>64</v>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>SM-S942N</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>SM-S948NK</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>S26U</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>초이스스페셜(130,000)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>SM-S947N</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>S26+</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>39</v>
+      <c r="G4" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>SM-S948N</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>S26U</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼(125,000)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>34</v>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -785,26 +932,32 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>SM-F966N</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>폴드7</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>프리미엄(125,000)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>139</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>SM-F766N</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>플립7</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -813,67 +966,1714 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>SM-S731N</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>S25 FE</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>프리미엄(125,000)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>-35</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>-5</v>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>SM-F966N</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>폴드7</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>SM-S931N</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>SM-S936N</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>S25+</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>SM-S938N</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>S25U</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>SM-S937N</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>S25엣지</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>SM-S731N</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>S25 FE</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>IP16_128GB</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>IPPL16_128GB</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 플러스</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>IPP16_128GB</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 프로</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>IPPM16_256GB</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 프로맥스 256G</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>IP17_256GB</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>아이폰 17</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>IP AIR_256GB</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 AIR</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>IPP17_256GB</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 PRO</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>IPPM17_256GB</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 프로맥스</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>SM-S942NK</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>SM-S947NK</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>S26+</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>SM-S948NK</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>S26U</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>SM-F766NK</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>플립7</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>SM-F966NK</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>폴드7</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>SM-S931NK</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>SM-S936NK</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>S25+</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>SM-S938NK</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>S25U</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>SM-S937NK</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>S25엣지</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>SM-S731NK</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>S25 FE</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>AIP16-128</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>아이폰16</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>초이스스페셜(130,000)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>-55</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F31" s="8" t="n">
         <v>-30</v>
       </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>※ 번이/기변 값(만원) = 공시지원금 기준 현금완납가 · 음수 = 페이백(고객 수령) · 양수 = 고객 부담 | 새 기종은 행(Row) 추가 | PK: (통신사+모델명+요금제)</t>
+      <c r="G31" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>AIP16PS-128</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 플러스</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-45</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>AIP16P-128</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 프로</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>AIP16PM-256</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 프로맥스 256G</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>AIP17-256</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>아이폰 17</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>AIPA-256</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 AIR</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>AIP17P-256</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 PRO</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>AIP17PM-256</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 프로맥스</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>초이스스페셜</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>SM-S942N</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>SM-S947N</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>S26+</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>SM-S948N</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>S26U</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>SM-F766N</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>플립7</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>SM-F966N</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>폴드7</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>SM-S931N</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>SM-S936N</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>S25+</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>SM-S938N</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>S25U</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>SM-S937N</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>S25엣지</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>SM-S731N</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>S25 FE</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>UIP16-128</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>UI16PL-128</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 플러스</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>UI16PR-128</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 프로</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>UI16PM-256</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>아이폰16 프로맥스 256G</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>UIP17-256</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>아이폰 17</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>UIPAIR-256</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 AIR</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>UI17PR-256</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 PRO</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>UI17PM-256</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>아이폰17 프로맥스</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>프리미어 슈퍼</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>※ 번이/기변 (만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록·고객 수령) · 양수=고객 부담(빨강)
+※ 인터넷/인터넷+TV (만원) = 결합 가입 시 추가 혜택 (전 행 공통 · 초록)
+※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼 (월요금은 어드민 등록)
+※ PK = (통신사+모델명+요금제) · 새 기종은 행 추가 · 컬럼은 고정</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -885,24 +2685,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 — 오프라인</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+          <t>📇 유심 시세 — 오프라인 · 5행</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>통신사</t>
@@ -920,12 +2723,27 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>요금제(월요금)</t>
+          <t>요금제</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>번이</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>기변</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>인터넷</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>인터넷+TV</t>
         </is>
       </c>
     </row>
@@ -935,136 +2753,174 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>세이브(33,000)</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>세이브</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
         <v>-40</v>
       </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>5G 슬림 4GB(45,000)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>5G 슬림 4GB</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>-15</v>
       </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>데이터33(33,000)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>데이터33</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>-15</v>
       </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>심플+(43,890)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>심플+</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>-30</v>
       </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>5G 에센셜(55,000)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>5G 에센셜</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>-40</v>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>※ MNP(번호이동)만 · 010 신규 제외 · 기변 공란 | 선택약정 25% 할인 (SK/KT 개통시 · LG 고객센터) | 실납 = 월요금 × 0.75 | 유심비 후납 (KT 선납 · 사은품에서 차감)</t>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>※ MNP(번호이동)만 · 010 신규 제외 · 기변 공란 (유심은 번이만)
+※ 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청) · 실납 = 월요금 × 0.75
+※ 유심비: SK/LG 다음 달 청구 · KT 선납(사은품에서 차감)
+※ 유지기간: SK M+6개월 · KT/LG 183일 (유지기간 내 회선 미유지/요금제 하향/단말 기변 시 전액 환수)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1076,22 +2932,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>📡 인터넷+TV 사은품 — 오프라인</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>종류</t>
@@ -1109,29 +2965,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>입력 후 저장</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>※ 결합 요금은 3사 표준 계산기 사용 (calculator.html) · 사은품만 등록 | 현금 페이백 지급</t>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>금액은 매장/온라인에서 지정</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>※ 결합 요금은 3사 표준 계산기 사용 (calculator.html) · 사은품만 등록 · 종류는 "현금"만</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -59,11 +59,11 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -133,6 +133,12 @@
         <bgColor rgb="00fef3c7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f3f4f6"/>
+        <bgColor rgb="00f3f4f6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -160,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,10 +183,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,14 +198,17 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -616,23 +625,23 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4. 값 단위: 만원 · 음수=페이백(고객 수령, 초록) · 양수=고객 부담(빨강)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>5. 인터넷/인터넷+TV 컬럼 = 결합 가입 시 추가 혜택 (전 행 공통)</t>
+          <t>4. 값 단위: 만원 · 음수=페이백(초록) · 양수=부담(빨강) · 빈칸=어드민 등록(회색)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>📊 포함 데이터</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>📊 포함 데이터 (정리3 원본)</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>· 무선(휴대폰): 3사 × 18종 = 54행</t>
         </is>
       </c>
     </row>
@@ -640,31 +649,31 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 무선(휴대폰): 3사 × 18종 = 54행 (SK 프리미엄 / KT 초이스스페셜 / LG 프리미어 슈퍼)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>· 유심: 오프라인 5행 / 온라인 8행 (본 파일은 오프라인)</t>
+          <t>· 유심: 3사 × 요금제별 = 8행 (SK 3 + KT 2 + LG 3) — 매장/온라인 구조 동일, 페이백 값만 다름</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>· 인터넷+TV 사은품: 현금 1종 (금액은 매장/온라인 지정)</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>📇 통신사별 유심 요금제</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>· SK: 세이브 / T플랜 안심2.5G / 5G 슬림</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>🔑 유심 정책 (핵심)</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>· KT: 5G 슬림 4GB / 5G 심플 30GB</t>
         </is>
       </c>
     </row>
@@ -672,23 +681,15 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>· 유심 변경 = 기기 그대로 · 유심만 다른 통신사로 교체</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>· MNP(번호이동)만 가능 · 010 신규 제외</t>
+          <t>· LG: 데이터33 / 심플+ / 5G 에센셜</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>· 선택약정 기반 월 요금 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>🔑 유심 정책</t>
         </is>
       </c>
     </row>
@@ -696,7 +697,7 @@
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품에서 차감)</t>
+          <t>· MNP 전용 · 010 신규 제외</t>
         </is>
       </c>
     </row>
@@ -704,7 +705,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
+          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
         </is>
       </c>
     </row>
@@ -712,31 +713,31 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>· 개통: 유심 수령 후 고객센터 수령 통화 → 개통 진행</t>
+          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ 주의</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>· 이 파일은 "오프라인" 전용 — 다른 채널과 섞지 말 것</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>· 개통: 유심 수령 후 고객센터 수령 통화 → 개통 진행</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>· 오프라인: 12개 매장 각자 복사해서 사용 (지역/협상력 반영)</t>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ 주의</t>
         </is>
       </c>
     </row>
@@ -744,7 +745,15 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· 온라인: 통합 1개 파일 (전국 동일 가격)</t>
+          <t>· 이 파일은 "오프라인" 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>· 오프라인: 12개 매장 각자 복사해서 사용 · 온라인: 통합 1개</t>
         </is>
       </c>
     </row>
@@ -2660,13 +2669,13 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="75" customHeight="1">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>※ 번이/기변 (만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록·고객 수령) · 양수=고객 부담(빨강)
-※ 인터넷/인터넷+TV (만원) = 결합 가입 시 추가 혜택 (전 행 공통 · 초록)
-※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼 (월요금은 어드민 등록)
-※ PK = (통신사+모델명+요금제) · 새 기종은 행 추가 · 컬럼은 고정</t>
+          <t>※ 번이/기변 (만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
+※ 인터넷/인터넷+TV (만원) = 결합 가입 시 추가 혜택 (전 행 공통 · 초록 배경)
+※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
+※ PK = (통신사+모델명+요금제) · 새 기종은 행 추가</t>
         </is>
       </c>
     </row>
@@ -2685,13 +2694,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2701,7 +2710,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 — 오프라인 · 5행</t>
+          <t>📇 유심 시세 — 오프라인 · 3사 × 요금제별 = 8행 (SK 3 + KT 2 + LG 3)</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2732,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>요금제</t>
+          <t>요금제 (월요금)</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -2765,13 +2774,13 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>세이브</t>
+          <t>세이브 (33,000)</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="F3" s="7" t="n"/>
+      <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="10" t="n">
         <v>40</v>
       </c>
@@ -2780,146 +2789,237 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>T플랜 안심2.5G (43,890)</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="14" t="inlineStr"/>
+      <c r="G4" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>5G 슬림 (55,000)</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>5G 슬림 4GB</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="n">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>5G 슬림 4GB (45,000)</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>-15</v>
       </c>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>5G 심플 30GB (69,000)</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>데이터33</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>데이터33 (33,000)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>-15</v>
       </c>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>심플+</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>심플+ (43,890)</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>-30</v>
       </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>유심-매장</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>5G 에센셜</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>5G 에센셜 (55,000)</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>※ MNP(번호이동)만 · 010 신규 제외 · 기변 공란 (유심은 번이만)
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>※ 매장·온라인 구조 동일 (8행) — 페이백 값만 다름 · 회색 셀은 어드민 등록 필요
+※ SK: 세이브 / T플랜 안심2.5G / 5G 슬림  |  KT: 5G 슬림 4GB / 5G 심플 30GB  |  LG: 데이터33 / 심플+ / 5G 에센셜
+※ MNP 전용 · 010 신규 제외 · 기변 공란 (유심은 번이만)
 ※ 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청) · 실납 = 월요금 × 0.75
-※ 유심비: SK/LG 다음 달 청구 · KT 선납(사은품에서 차감)
-※ 유지기간: SK M+6개월 · KT/LG 183일 (유지기간 내 회선 미유지/요금제 하향/단말 기변 시 전액 환수)</t>
+※ 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감) · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2980,7 +3080,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>※ 결합 요금은 3사 표준 계산기 사용 (calculator.html) · 사은품만 등록 · 종류는 "현금"만</t>
+          <t>※ 결합 요금은 3사 표준 계산기 사용 · 사은품 종류는 "현금"만</t>
         </is>
       </c>
     </row>

--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -609,7 +609,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2. 컬럼은 고정 · 새 기종/요금제는 "행(Row) 추가"로 관리</t>
+          <t>2. 컬럼 고정 · 새 기종/요금제는 "행 추가"로 관리</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3. PK = (통신사 + 모델명 + 요금제) — 업로드 시 동일 조합 덮어쓰기</t>
+          <t>3. PK = (통신사+모델명+요금제) · 업로드 시 동일 조합 덮어쓰기</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· 무선(휴대폰): 3사 × 18종 = 54행</t>
+          <t>· 무선(휴대폰): 3사 × 18종 = 54행 (정리3 원본)</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 유심: 3사 × 요금제별 = 8행 (SK 3 + KT 2 + LG 3) — 매장/온라인 구조 동일, 페이백 값만 다름</t>
+          <t>· 유심: 3사 × 3종 = 9행 (매장/온라인 구조 동일, 페이백 값만 다름)</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>📇 통신사별 유심 요금제</t>
+          <t>📇 통신사별 유심 요금제 (3사 × 3종 = 9개)</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>· SK: 세이브 / T플랜 안심2.5G / 5G 슬림</t>
+          <t>· SK: 5GX 슬림(33,000) / 베이직 플러스(45,000) / 5GX 레귤러(55,000)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>· KT: 5G 슬림 4GB / 5G 심플 30GB</t>
+          <t>· KT: 5G 슬림(37,000) / 5G 심플(50,000) / 5G 비디오(69,000)</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>· LG: 데이터33 / 심플+ / 5G 에센셜</t>
+          <t>· LG: 5G 슬림+(33,000) / 5G 스탠다드(61,000) / 5G 프리미어 레귤러(85,000)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· 오프라인: 12개 매장 각자 복사해서 사용 · 온라인: 통합 1개</t>
+          <t>· 오프라인: 12개 매장 각자 복사 · 온라인: 통합 1개</t>
         </is>
       </c>
     </row>
@@ -2669,13 +2669,13 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" ht="75" customHeight="1">
+    <row r="58" ht="80" customHeight="1">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>※ 번이/기변 (만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
-※ 인터넷/인터넷+TV (만원) = 결합 가입 시 추가 혜택 (전 행 공통 · 초록 배경)
+          <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
+※ 인터넷/인터넷+TV(만원) = 결합 가입 시 추가 혜택 (전 행 공통 · 초록 배경)
 ※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
-※ PK = (통신사+모델명+요금제) · 새 기종은 행 추가</t>
+※ PK=(통신사+모델명+요금제) · 새 기종은 행 추가</t>
         </is>
       </c>
     </row>
@@ -2694,13 +2694,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2710,7 +2710,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 — 오프라인 · 3사 × 요금제별 = 8행 (SK 3 + KT 2 + LG 3)</t>
+          <t>📇 유심 시세 — 오프라인 · 3사 × 3종 = 9행</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,10 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>세이브 (33,000)</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>-40</v>
-      </c>
+          <t>5GX 슬림 (33,000)</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr"/>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="10" t="n">
         <v>40</v>
@@ -2806,7 +2804,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>T플랜 안심2.5G (43,890)</t>
+          <t>베이직 플러스 (45,000)</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr"/>
@@ -2836,7 +2834,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>5G 슬림 (55,000)</t>
+          <t>5GX 레귤러 (55,000)</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr"/>
@@ -2866,12 +2864,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>5G 슬림 4GB (45,000)</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-15</v>
-      </c>
+          <t>5G 슬림 (37,000)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
       <c r="F6" s="14" t="inlineStr"/>
       <c r="G6" s="10" t="n">
         <v>40</v>
@@ -2898,7 +2894,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>5G 심플 30GB (69,000)</t>
+          <t>5G 심플 (50,000)</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr"/>
@@ -2911,9 +2907,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>LG</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>KT</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2928,12 +2924,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>데이터33 (33,000)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-15</v>
-      </c>
+          <t>5G 비디오 (69,000)</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr"/>
       <c r="F8" s="14" t="inlineStr"/>
       <c r="G8" s="10" t="n">
         <v>40</v>
@@ -2960,12 +2954,10 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>심플+ (43,890)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-30</v>
-      </c>
+          <t>5G 슬림+ (33,000)</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="10" t="n">
         <v>40</v>
@@ -2992,12 +2984,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>5G 에센셜 (55,000)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-40</v>
-      </c>
+          <t>5G 스탠다드 (61,000)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
       <c r="F10" s="14" t="inlineStr"/>
       <c r="G10" s="10" t="n">
         <v>40</v>
@@ -3006,20 +2996,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>※ 매장·온라인 구조 동일 (8행) — 페이백 값만 다름 · 회색 셀은 어드민 등록 필요
-※ SK: 세이브 / T플랜 안심2.5G / 5G 슬림  |  KT: 5G 슬림 4GB / 5G 심플 30GB  |  LG: 데이터33 / 심플+ / 5G 에센셜
-※ MNP 전용 · 010 신규 제외 · 기변 공란 (유심은 번이만)
-※ 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청) · 실납 = 월요금 × 0.75
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>유심-매장</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>5G 프리미어 레귤러 (85,000)</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>※ 매장·온라인 구조 동일 (9행) — 페이백 값만 다름 · 빈칸(회색)=어드민 등록
+※ SK: 5GX 슬림(33,000) / 베이직 플러스(45,000) / 5GX 레귤러(55,000)
+※ KT: 5G 슬림(37,000) / 5G 심플(50,000) / 5G 비디오(69,000)
+※ LG: 5G 슬림+(33,000) / 5G 스탠다드(61,000) / 5G 프리미어 레귤러(85,000)
+※ MNP 전용 · 010 신규 제외 · 기변 공란 · 선택약정 25% 할인 (SK/KT 개통시·LG 고객센터)
 ※ 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감) · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -107,12 +107,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00fee2e2"/>
         <bgColor rgb="00fee2e2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00d1fae5"/>
-        <bgColor rgb="00d1fae5"/>
       </patternFill>
     </fill>
     <fill>
@@ -166,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,19 +189,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -641,7 +632,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· 무선(휴대폰): 3사 × 18종 = 54행 (정리3 원본)</t>
+          <t>· 무선(휴대폰): 3사 × 18종 = 54행 (컬럼 6개)</t>
         </is>
       </c>
     </row>
@@ -649,7 +640,7 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 유심: 3사 × 3종 = 9행 (매장/온라인 구조 동일, 페이백 값만 다름)</t>
+          <t>· 유심: 3사 × 3종 = 9행 (매장/온라인 구조 동일)</t>
         </is>
       </c>
     </row>
@@ -657,7 +648,7 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>📇 통신사별 유심 요금제 (3사 × 3종 = 9개)</t>
+          <t>📇 통신사별 유심 요금제 (3사 × 3종)</t>
         </is>
       </c>
     </row>
@@ -771,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -780,8 +771,6 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -822,16 +811,6 @@
           <t>기변</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>인터넷</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>인터넷+TV</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -860,12 +839,6 @@
       <c r="F3" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -894,12 +867,6 @@
       <c r="F4" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="G4" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -928,12 +895,6 @@
       <c r="F5" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -962,12 +923,6 @@
       <c r="F6" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="G6" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -996,12 +951,6 @@
       <c r="F7" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1030,12 +979,6 @@
       <c r="F8" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1064,12 +1007,6 @@
       <c r="F9" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1098,12 +1035,6 @@
       <c r="F10" s="9" t="n">
         <v>114</v>
       </c>
-      <c r="G10" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1132,12 +1063,6 @@
       <c r="F11" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1166,12 +1091,6 @@
       <c r="F12" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1200,12 +1119,6 @@
       <c r="F13" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1234,12 +1147,6 @@
       <c r="F14" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="G14" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1268,12 +1175,6 @@
       <c r="F15" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1302,12 +1203,6 @@
       <c r="F16" s="9" t="n">
         <v>129</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1336,12 +1231,6 @@
       <c r="F17" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1370,12 +1259,6 @@
       <c r="F18" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1404,12 +1287,6 @@
       <c r="F19" s="9" t="n">
         <v>104</v>
       </c>
-      <c r="G19" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1438,15 +1315,9 @@
       <c r="F20" s="9" t="n">
         <v>144</v>
       </c>
-      <c r="G20" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1472,15 +1343,9 @@
       <c r="F21" s="8" t="n">
         <v>-15</v>
       </c>
-      <c r="G21" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1506,15 +1371,9 @@
       <c r="F22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1540,15 +1399,9 @@
       <c r="F23" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="G23" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1574,15 +1427,9 @@
       <c r="F24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1608,15 +1455,9 @@
       <c r="F25" s="9" t="n">
         <v>104</v>
       </c>
-      <c r="G25" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1642,15 +1483,9 @@
       <c r="F26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G26" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1676,15 +1511,9 @@
       <c r="F27" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="G27" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1710,15 +1539,9 @@
       <c r="F28" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="G28" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1744,15 +1567,9 @@
       <c r="F29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1778,15 +1595,9 @@
       <c r="F30" s="8" t="n">
         <v>-25</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1812,15 +1623,9 @@
       <c r="F31" s="8" t="n">
         <v>-30</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H31" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1846,15 +1651,9 @@
       <c r="F32" s="8" t="n">
         <v>-20</v>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1880,15 +1679,9 @@
       <c r="F33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H33" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1914,15 +1707,9 @@
       <c r="F34" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="G34" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1948,15 +1735,9 @@
       <c r="F35" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G35" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -1982,15 +1763,9 @@
       <c r="F36" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="G36" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -2016,15 +1791,9 @@
       <c r="F37" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="G37" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H37" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -2050,15 +1819,9 @@
       <c r="F38" s="9" t="n">
         <v>124</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2084,15 +1847,9 @@
       <c r="F39" s="8" t="n">
         <v>-20</v>
       </c>
-      <c r="G39" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H39" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2118,15 +1875,9 @@
       <c r="F40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2152,15 +1903,9 @@
       <c r="F41" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="G41" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H41" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2186,15 +1931,9 @@
       <c r="F42" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="G42" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H42" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2220,15 +1959,9 @@
       <c r="F43" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="G43" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2254,15 +1987,9 @@
       <c r="F44" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="G44" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2288,15 +2015,9 @@
       <c r="F45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="G45" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H45" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2322,15 +2043,9 @@
       <c r="F46" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="G46" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2356,15 +2071,9 @@
       <c r="F47" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H47" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2390,15 +2099,9 @@
       <c r="F48" s="8" t="n">
         <v>-15</v>
       </c>
-      <c r="G48" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2424,15 +2127,9 @@
       <c r="F49" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="G49" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H49" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2458,15 +2155,9 @@
       <c r="F50" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H50" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2492,15 +2183,9 @@
       <c r="F51" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="G51" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H51" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2526,15 +2211,9 @@
       <c r="F52" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="G52" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H52" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2560,15 +2239,9 @@
       <c r="F53" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G53" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2594,15 +2267,9 @@
       <c r="F54" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="G54" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2628,15 +2295,9 @@
       <c r="F55" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="G55" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H55" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2662,27 +2323,21 @@
       <c r="F56" s="9" t="n">
         <v>114</v>
       </c>
-      <c r="G56" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="58" ht="80" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
-※ 인터넷/인터넷+TV(만원) = 결합 가입 시 추가 혜택 (전 행 공통 · 초록 배경)
 ※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
-※ PK=(통신사+모델명+요금제) · 새 기종은 행 추가</t>
+※ PK=(통신사+모델명+요금제) · 새 기종은 행 추가
+※ 인터넷+TV 결합 혜택은 ③ 시트에서 별도 관리</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2694,7 +2349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2703,8 +2358,6 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2745,16 +2398,6 @@
           <t>기변</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>인터넷</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>인터넷+TV</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2777,14 +2420,8 @@
           <t>5GX 슬림 (33,000)</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr"/>
-      <c r="F3" s="14" t="inlineStr"/>
-      <c r="G3" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="13" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2807,14 +2444,8 @@
           <t>베이직 플러스 (45,000)</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr"/>
-      <c r="F4" s="14" t="inlineStr"/>
-      <c r="G4" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2837,17 +2468,11 @@
           <t>5GX 레귤러 (55,000)</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr"/>
-      <c r="F5" s="14" t="inlineStr"/>
-      <c r="G5" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -2867,17 +2492,11 @@
           <t>5G 슬림 (37,000)</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
-      <c r="F6" s="14" t="inlineStr"/>
-      <c r="G6" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -2897,17 +2516,11 @@
           <t>5G 심플 (50,000)</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
@@ -2927,17 +2540,11 @@
           <t>5G 비디오 (69,000)</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr"/>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2957,17 +2564,11 @@
           <t>5G 슬림+ (33,000)</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr"/>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2987,17 +2588,11 @@
           <t>5G 스탠다드 (61,000)</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-      <c r="G10" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -3017,31 +2612,25 @@
           <t>5G 프리미어 레귤러 (85,000)</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>70</v>
-      </c>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>※ 매장·온라인 구조 동일 (9행) — 페이백 값만 다름 · 빈칸(회색)=어드민 등록
 ※ SK: 5GX 슬림(33,000) / 베이직 플러스(45,000) / 5GX 레귤러(55,000)
 ※ KT: 5G 슬림(37,000) / 5G 심플(50,000) / 5G 비디오(69,000)
 ※ LG: 5G 슬림+(33,000) / 5G 스탠다드(61,000) / 5G 프리미어 레귤러(85,000)
 ※ MNP 전용 · 010 신규 제외 · 기변 공란 · 선택약정 25% 할인 (SK/KT 개통시·LG 고객센터)
-※ 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감) · 유지기간: SK M+6 / KT·LG 183일</t>
+※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3099,7 +2688,7 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>※ 결합 요금은 3사 표준 계산기 사용 · 사은품 종류는 "현금"만</t>
         </is>

--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -133,6 +133,24 @@
         <bgColor rgb="00f3f4f6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00dc2626"/>
+        <bgColor rgb="00dc2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563eb"/>
+        <bgColor rgb="002563eb"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e40981"/>
+        <bgColor rgb="00e40981"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -160,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -199,6 +217,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -608,7 +644,7 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3. PK = (통신사+모델명+요금제) · 업로드 시 동일 조합 덮어쓰기</t>
+          <t>3. PK = (통신사+모델명+요금제) · 업로드 시 덮어쓰기</t>
         </is>
       </c>
     </row>
@@ -624,7 +660,7 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>📊 포함 데이터</t>
+          <t>📊 시트 구조</t>
         </is>
       </c>
     </row>
@@ -632,7 +668,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· 무선(휴대폰): 3사 × 18종 = 54행 (컬럼 6개)</t>
+          <t>· ① 무선(휴대폰): 6컬럼 (통신사/모델명/펫네임/요금제/번이/기변) · 54행</t>
         </is>
       </c>
     </row>
@@ -640,23 +676,23 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 유심: 3사 × 3종 = 9행 (매장/온라인 구조 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>📇 통신사별 유심 요금제 (3사 × 3종)</t>
+          <t>· ② 유심: 5컬럼 (통신사/모델명/펫네임/요금제/번이) · 9행 · 기변 없음 (MNP 전용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>· ③ 인터넷+TV 사은품: 3컬럼 (종류/금액/비고) · 현금만</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>· SK: 5GX 슬림(33,000) / 베이직 플러스(45,000) / 5GX 레귤러(55,000)</t>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>📇 통신사별 유심 요금제</t>
         </is>
       </c>
     </row>
@@ -664,7 +700,7 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>· KT: 5G 슬림(37,000) / 5G 심플(50,000) / 5G 비디오(69,000)</t>
+          <t>· SK: 5GX 슬림(33) / 베이직 플러스(45) / 5GX 레귤러(55)</t>
         </is>
       </c>
     </row>
@@ -672,23 +708,23 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>· LG: 5G 슬림+(33,000) / 5G 스탠다드(61,000) / 5G 프리미어 레귤러(85,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>🔑 유심 정책</t>
+          <t>· KT: 5G 슬림(37) / 5G 심플(50) / 5G 비디오(69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>· LG: 5G 슬림+(33) / 5G 스탠다드(61) / 5G 프리미어 레귤러(85)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>· MNP 전용 · 010 신규 제외</t>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>🔑 유심 정책</t>
         </is>
       </c>
     </row>
@@ -696,7 +732,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
+          <t>· MNP 전용 · 010 신규 제외 · 기변 없음</t>
         </is>
       </c>
     </row>
@@ -704,7 +740,7 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감)</t>
+          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
         </is>
       </c>
     </row>
@@ -712,7 +748,7 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
+          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감)</t>
         </is>
       </c>
     </row>
@@ -720,29 +756,37 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>· 개통: 유심 수령 후 고객센터 수령 통화 → 개통 진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ 주의</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>· 이 파일은 "오프라인" 전용</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ 주의</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>· 이 파일은 "오프라인" 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>· 오프라인: 12개 매장 각자 복사 · 온라인: 통합 1개</t>
         </is>
@@ -2324,7 +2368,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" ht="80" customHeight="1">
+    <row r="58" ht="85" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
           <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
@@ -2349,15 +2393,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2393,11 +2436,6 @@
           <t>번이</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>기변</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2421,7 +2459,6 @@
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2445,7 +2482,6 @@
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr"/>
-      <c r="F4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2469,7 +2505,6 @@
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -2493,7 +2528,6 @@
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -2517,7 +2551,6 @@
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -2541,7 +2574,6 @@
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -2565,7 +2597,6 @@
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -2589,7 +2620,6 @@
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -2613,24 +2643,22 @@
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="13" t="inlineStr"/>
-    </row>
-    <row r="13" ht="80" customHeight="1">
+    </row>
+    <row r="13" ht="85" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>※ 매장·온라인 구조 동일 (9행) — 페이백 값만 다름 · 빈칸(회색)=어드민 등록
-※ SK: 5GX 슬림(33,000) / 베이직 플러스(45,000) / 5GX 레귤러(55,000)
-※ KT: 5G 슬림(37,000) / 5G 심플(50,000) / 5G 비디오(69,000)
-※ LG: 5G 슬림+(33,000) / 5G 스탠다드(61,000) / 5G 프리미어 레귤러(85,000)
-※ MNP 전용 · 010 신규 제외 · 기변 공란 · 선택약정 25% 할인 (SK/KT 개통시·LG 고객센터)
+          <t>※ 유심은 MNP(번호이동) 전용 → 기변 없음 · 번이만 입력
+※ 매장·온라인 구조 동일 (9행) — 페이백 값만 다름 · 빈칸(회색)=어드민 등록
+※ SK: 5GX 슬림(33)/베이직 플러스(45)/5GX 레귤러(55) | KT: 5G 슬림(37)/5G 심플(50)/5G 비디오(69) | LG: 5G 슬림+(33)/5G 스탠다드(61)/5G 프리미어 레귤러(85)
+※ 선택약정 25% 할인 (SK/KT 개통시·LG 고객센터) · 실납 = 월요금 × 0.75
 ※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2642,18 +2670,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📡 인터넷+TV 사은품 — 오프라인</t>
+          <t>📡 인터넷+TV 사은품 — 오프라인 · 통신사별 금액 등록</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2693,22 @@
           <t>종류</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>금액(만원)</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2680,24 +2720,26 @@
           <t>현금</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr"/>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>금액은 매장/온라인에서 지정</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+      <c r="B3" s="17" t="inlineStr"/>
+      <c r="C3" s="18" t="inlineStr"/>
+      <c r="D3" s="19" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>통신사별 페이백 금액 (만원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 결합 요금은 3사 표준 계산기 사용 · 사은품 종류는 "현금"만</t>
+          <t>※ 사은품 = 현금 페이백 (통신사별 다름) · 결합 요금은 3사 표준 계산기 사용 · 금액 단위: 만원</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -620,7 +620,7 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>📌 사용법</t>
+          <t>📌 컬럼 구조 (flow-store-price.html STEP 9 기준)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1. 시트별로 ① 무선 · ② 유심 · ③ 인터넷+TV 사은품 입력</t>
+          <t>· ① 무선: 통신사 / 펫네임 / 요금제(월요금) / 번이 / 기변</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2. 컬럼 고정 · 새 기종/요금제는 "행 추가"로 관리</t>
+          <t>· ② 유심: 통신사 / 요금제(월요금) / 25%↓실납 / 번이 (펫네임/기변 없음)</t>
         </is>
       </c>
     </row>
@@ -644,23 +644,23 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3. PK = (통신사+모델명+요금제) · 업로드 시 덮어쓰기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>4. 값 단위: 만원 · 음수=페이백(초록) · 양수=부담(빨강) · 빈칸=어드민 등록(회색)</t>
+          <t>· ③ 인터넷+TV 사은품: 종류 / SK / KT / LG / 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>📊 데이터</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>📊 시트 구조</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>· 무선: 54행 (3사 × 18종) · 요금제: SK 프리미엄 / KT 초이스스페셜 / LG 프리미어 슈퍼</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· ① 무선(휴대폰): 6컬럼 (통신사/모델명/펫네임/요금제/번이/기변) · 54행</t>
+          <t>· 유심: 9행 (3사 × 3종) · 매장/온라인 구조 동일, 페이백 값만 다름</t>
         </is>
       </c>
     </row>
@@ -676,23 +676,23 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· ② 유심: 5컬럼 (통신사/모델명/펫네임/요금제/번이) · 9행 · 기변 없음 (MNP 전용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>· ③ 인터넷+TV 사은품: 3컬럼 (종류/금액/비고) · 현금만</t>
+          <t>· 인터넷+TV 사은품: 현금만 · 3사별 금액 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>📇 유심 요금제 (3사 × 3종)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>📇 통신사별 유심 요금제</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>· SK: 5GX 슬림(33,000) / 베이직 플러스(45,000) / 5GX 레귤러(55,000)</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>· SK: 5GX 슬림(33) / 베이직 플러스(45) / 5GX 레귤러(55)</t>
+          <t>· KT: 5G 슬림(37,000) / 5G 심플(50,000) / 5G 비디오(69,000)</t>
         </is>
       </c>
     </row>
@@ -708,23 +708,23 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>· KT: 5G 슬림(37) / 5G 심플(50) / 5G 비디오(69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>· LG: 5G 슬림+(33) / 5G 스탠다드(61) / 5G 프리미어 레귤러(85)</t>
+          <t>· LG: 5G 슬림+(33,000) / 5G 스탠다드(61,000) / 5G 프리미어 레귤러(85,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>🔑 유심 정책</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>🔑 유심 정책</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>· MNP 전용 · 010 신규 제외 · 기변 없음</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>· MNP 전용 · 010 신규 제외 · 기변 없음</t>
+          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청) · 실납 = 월요금 × 0.75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
+          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6개월 · KT/LG 183일</t>
         </is>
       </c>
     </row>
@@ -748,31 +748,31 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>· 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>· 유지기간: SK M+6개월 · KT/LG 183일</t>
+          <t>· 개통: 유심 수령 후 고객센터 수령 통화 → 개통 진행</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>· 개통: 유심 수령 후 고객센터 수령 통화 → 개통 진행</t>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ 입력 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>· 값 단위: 만원 · 음수=페이백(초록) · 양수=부담(빨강) · 빈칸=어드민 등록(회색)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ 주의</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>· 이 파일은 "오프라인" 전용 · 오프라인: 12개 매장 각자 복사 · 온라인: 통합 1개</t>
         </is>
       </c>
     </row>
@@ -780,15 +780,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· 이 파일은 "오프라인" 전용</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>· 오프라인: 12개 매장 각자 복사 · 온라인: 통합 1개</t>
+          <t>· PK=(통신사+펫네임+요금제 또는 통신사+요금제) · 새 기종은 행 추가</t>
         </is>
       </c>
     </row>
@@ -806,21 +798,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📱 무선(휴대폰) 시세 — 오프라인 · 3사 × 18종 = 54행</t>
+          <t>📱 무선(휴대폰) 시세 — 오프라인 · 54행</t>
         </is>
       </c>
     </row>
@@ -832,25 +823,20 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>모델명</t>
+          <t>펫네임</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>펫네임</t>
+          <t>요금제(월요금)</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>요금제</t>
+          <t>번이</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>번이</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>기변</t>
         </is>
@@ -864,23 +850,18 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>SM-S942N</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
         <v>-10</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="E3" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -892,23 +873,18 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>SM-S947N</t>
+          <t>S26+</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>S26+</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" s="9" t="n">
         <v>34</v>
       </c>
     </row>
@@ -920,23 +896,18 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>SM-S948N</t>
+          <t>S26U</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>S26U</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>44</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F5" s="9" t="n">
         <v>64</v>
       </c>
     </row>
@@ -948,23 +919,18 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>SM-F766N</t>
+          <t>플립7</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>플립7</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F6" s="9" t="n">
         <v>44</v>
       </c>
     </row>
@@ -976,23 +942,18 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>SM-F966N</t>
+          <t>폴드7</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>폴드7</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>127</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="F7" s="9" t="n">
         <v>139</v>
       </c>
     </row>
@@ -1004,23 +965,18 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>SM-S931N</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="9" t="n">
         <v>59</v>
       </c>
     </row>
@@ -1032,23 +988,18 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>SM-S936N</t>
+          <t>S25+</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>S25+</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="F9" s="9" t="n">
         <v>79</v>
       </c>
     </row>
@@ -1060,23 +1011,18 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>SM-S938N</t>
+          <t>S25U</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>S25U</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>59</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="F10" s="9" t="n">
         <v>114</v>
       </c>
     </row>
@@ -1088,23 +1034,18 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SM-S937N</t>
+          <t>S25엣지</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>S25엣지</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>39</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="F11" s="9" t="n">
         <v>37</v>
       </c>
     </row>
@@ -1116,23 +1057,18 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>SM-S731N</t>
+          <t>S25 FE</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>S25 FE</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>-35</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>-35</v>
-      </c>
-      <c r="F12" s="8" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -1144,23 +1080,18 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>IP16_128GB</t>
+          <t>아이폰16</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>아이폰16</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F13" s="9" t="n">
         <v>59</v>
       </c>
     </row>
@@ -1172,23 +1103,18 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>IPPL16_128GB</t>
+          <t>아이폰16 플러스</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 플러스</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>74</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>74</v>
-      </c>
-      <c r="F14" s="9" t="n">
         <v>79</v>
       </c>
     </row>
@@ -1200,23 +1126,18 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>IPP16_128GB</t>
+          <t>아이폰16 프로</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 프로</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>49</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="F15" s="9" t="n">
         <v>79</v>
       </c>
     </row>
@@ -1228,23 +1149,18 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>IPPM16_256GB</t>
+          <t>아이폰16 프로맥스 256G</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 프로맥스 256G</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>124</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>124</v>
-      </c>
-      <c r="F16" s="9" t="n">
         <v>129</v>
       </c>
     </row>
@@ -1256,23 +1172,18 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>IP17_256GB</t>
+          <t>아이폰 17</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>아이폰 17</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="9" t="n">
         <v>54</v>
       </c>
     </row>
@@ -1284,23 +1195,18 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>IP AIR_256GB</t>
+          <t>아이폰17 AIR</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 AIR</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>49</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="F18" s="9" t="n">
         <v>84</v>
       </c>
     </row>
@@ -1312,23 +1218,18 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>IPP17_256GB</t>
+          <t>아이폰17 PRO</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 PRO</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>59</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="F19" s="9" t="n">
         <v>104</v>
       </c>
     </row>
@@ -1340,23 +1241,18 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>IPPM17_256GB</t>
+          <t>아이폰17 프로맥스</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 프로맥스</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>프리미엄</t>
-        </is>
+          <t>프리미엄(125,000)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>109</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>109</v>
-      </c>
-      <c r="F20" s="9" t="n">
         <v>144</v>
       </c>
     </row>
@@ -1368,23 +1264,18 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>SM-S942NK</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>-20</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>-20</v>
-      </c>
-      <c r="F21" s="8" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -1396,23 +1287,18 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>SM-S947NK</t>
+          <t>S26+</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>S26+</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n">
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1424,23 +1310,18 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>SM-S948NK</t>
+          <t>S26U</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>S26U</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="F23" s="9" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1452,23 +1333,18 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>SM-F766NK</t>
+          <t>플립7</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>플립7</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1480,23 +1356,18 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>SM-F966NK</t>
+          <t>폴드7</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>폴드7</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>99</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>99</v>
-      </c>
-      <c r="F25" s="9" t="n">
         <v>104</v>
       </c>
     </row>
@@ -1508,23 +1379,18 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>SM-S931NK</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="E26" s="9" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1536,23 +1402,18 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>SM-S936NK</t>
+          <t>S25+</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>S25+</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F27" s="9" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1564,23 +1425,18 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>SM-S938NK</t>
+          <t>S25U</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>S25U</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>54</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="F28" s="9" t="n">
         <v>74</v>
       </c>
     </row>
@@ -1592,23 +1448,18 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>SM-S937NK</t>
+          <t>S25엣지</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>S25엣지</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="E29" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1620,23 +1471,18 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>SM-S731NK</t>
+          <t>S25 FE</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>S25 FE</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>-40</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>-40</v>
-      </c>
-      <c r="F30" s="8" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -1648,23 +1494,18 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>AIP16-128</t>
+          <t>아이폰16</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>아이폰16</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>-55</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-55</v>
-      </c>
-      <c r="F31" s="8" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -1676,23 +1517,18 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>AIP16PS-128</t>
+          <t>아이폰16 플러스</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 플러스</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>-45</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-45</v>
-      </c>
-      <c r="F32" s="8" t="n">
         <v>-20</v>
       </c>
     </row>
@@ -1704,23 +1540,18 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>AIP16P-128</t>
+          <t>아이폰16 프로</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 프로</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
         <v>-25</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="E33" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1732,23 +1563,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>AIP16PM-256</t>
+          <t>아이폰16 프로맥스 256G</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 프로맥스 256G</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F34" s="9" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1760,23 +1586,18 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>AIP17-256</t>
+          <t>아이폰 17</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>아이폰 17</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="E35" s="9" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1788,23 +1609,18 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>AIPA-256</t>
+          <t>아이폰17 AIR</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 AIR</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="F36" s="9" t="n">
         <v>54</v>
       </c>
     </row>
@@ -1816,23 +1632,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>AIP17P-256</t>
+          <t>아이폰17 PRO</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 PRO</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>59</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="F37" s="9" t="n">
         <v>79</v>
       </c>
     </row>
@@ -1844,23 +1655,18 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>AIP17PM-256</t>
+          <t>아이폰17 프로맥스</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 프로맥스</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>초이스스페셜</t>
-        </is>
+          <t>초이스스페셜(130,000)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>94</v>
-      </c>
-      <c r="F38" s="9" t="n">
         <v>124</v>
       </c>
     </row>
@@ -1872,23 +1678,18 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>SM-S942N</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>S26</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>-25</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-25</v>
-      </c>
-      <c r="F39" s="8" t="n">
         <v>-20</v>
       </c>
     </row>
@@ -1900,23 +1701,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>SM-S947N</t>
+          <t>S26+</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>S26+</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="E40" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1928,23 +1724,18 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>SM-S948N</t>
+          <t>S26U</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>S26U</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>29</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F41" s="9" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1956,25 +1747,20 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>SM-F766N</t>
+          <t>플립7</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>플립7</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>-5</v>
       </c>
       <c r="E42" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>-5</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -1984,25 +1770,20 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SM-F966N</t>
+          <t>폴드7</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>폴드7</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="E43" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="F43" s="9" t="n">
-        <v>94</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -2012,23 +1793,18 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>SM-S931N</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>S25</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>19</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F44" s="9" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2040,23 +1816,18 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SM-S936N</t>
+          <t>S25+</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>S25+</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>39</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="F45" s="9" t="n">
         <v>44</v>
       </c>
     </row>
@@ -2068,23 +1839,18 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>SM-S938N</t>
+          <t>S25U</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>S25U</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>74</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>74</v>
-      </c>
-      <c r="F46" s="9" t="n">
         <v>78</v>
       </c>
     </row>
@@ -2096,23 +1862,18 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>SM-S937N</t>
+          <t>S25엣지</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>S25엣지</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
         <v>-20</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="E47" s="9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2124,23 +1885,18 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>SM-S731N</t>
+          <t>S25 FE</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>S25 FE</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>-50</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-50</v>
-      </c>
-      <c r="F48" s="8" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -2152,23 +1908,18 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>UIP16-128</t>
+          <t>아이폰16</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>아이폰16</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="E49" s="9" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2180,23 +1931,18 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>UI16PL-128</t>
+          <t>아이폰16 플러스</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 플러스</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="E50" s="9" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2208,23 +1954,18 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>UI16PR-128</t>
+          <t>아이폰16 프로</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 프로</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
         <v>-5</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="E51" s="9" t="n">
         <v>44</v>
       </c>
     </row>
@@ -2236,23 +1977,18 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>UI16PM-256</t>
+          <t>아이폰16 프로맥스 256G</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>아이폰16 프로맥스 256G</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>29</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F52" s="9" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2264,23 +2000,18 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>UIP17-256</t>
+          <t>아이폰 17</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>아이폰 17</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
         <v>-15</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="E53" s="9" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2292,23 +2023,18 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>UIPAIR-256</t>
+          <t>아이폰17 AIR</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 AIR</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="n">
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="E54" s="9" t="n">
         <v>49</v>
       </c>
     </row>
@@ -2320,23 +2046,18 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>UI17PR-256</t>
+          <t>아이폰17 PRO</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 PRO</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>34</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="F55" s="9" t="n">
         <v>69</v>
       </c>
     </row>
@@ -2348,40 +2069,34 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>UI17PM-256</t>
+          <t>아이폰17 프로맥스</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>아이폰17 프로맥스</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>프리미어 슈퍼</t>
-        </is>
+          <t>프리미어 슈퍼(125,000)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>89</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>89</v>
-      </c>
-      <c r="F56" s="9" t="n">
         <v>114</v>
       </c>
     </row>
-    <row r="58" ht="85" customHeight="1">
+    <row r="58" ht="80" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
           <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
-※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
-※ PK=(통신사+모델명+요금제) · 새 기종은 행 추가
-※ 인터넷+TV 결합 혜택은 ③ 시트에서 별도 관리</t>
+※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼 (월요금 원 단위)
+※ 새 기종은 행 추가 · 컬럼 고정</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2393,20 +2108,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 — 오프라인 · 3사 × 3종 = 9행</t>
+          <t>📇 유심 시세 — 오프라인 · 9행 (3사 × 3종)</t>
         </is>
       </c>
     </row>
@@ -2418,20 +2132,15 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>모델명</t>
+          <t>요금제(월요금)</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>펫네임</t>
+          <t>25%↓실납</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>요금제 (월요금)</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>번이</t>
         </is>
@@ -2445,20 +2154,15 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5GX 슬림(33,000)</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>5GX 슬림 (33,000)</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr"/>
+          <t>24,750</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2468,20 +2172,15 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>베이직 플러스(45,000)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>베이직 플러스 (45,000)</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr"/>
+          <t>33,750</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2491,20 +2190,15 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5GX 레귤러(55,000)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>5GX 레귤러 (55,000)</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr"/>
+          <t>41,250</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -2514,20 +2208,15 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5G 슬림(37,000)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>5G 슬림 (37,000)</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr"/>
+          <t>27,750</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -2537,20 +2226,15 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5G 심플(50,000)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>5G 심플 (50,000)</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr"/>
+          <t>37,500</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -2560,20 +2244,15 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5G 비디오(69,000)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>5G 비디오 (69,000)</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr"/>
+          <t>51,750</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -2583,20 +2262,15 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5G 슬림+(33,000)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>5G 슬림+ (33,000)</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr"/>
+          <t>24,750</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -2606,20 +2280,15 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5G 스탠다드(61,000)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>5G 스탠다드 (61,000)</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr"/>
+          <t>45,750</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -2629,36 +2298,30 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
+          <t>5G 프리미어 레귤러(85,000)</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>유심-매장</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>5G 프리미어 레귤러 (85,000)</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr"/>
-    </row>
-    <row r="13" ht="85" customHeight="1">
+          <t>63,750</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr"/>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>※ 유심은 MNP(번호이동) 전용 → 기변 없음 · 번이만 입력
-※ 매장·온라인 구조 동일 (9행) — 페이백 값만 다름 · 빈칸(회색)=어드민 등록
-※ SK: 5GX 슬림(33)/베이직 플러스(45)/5GX 레귤러(55) | KT: 5G 슬림(37)/5G 심플(50)/5G 비디오(69) | LG: 5G 슬림+(33)/5G 스탠다드(61)/5G 프리미어 레귤러(85)
-※ 선택약정 25% 할인 (SK/KT 개통시·LG 고객센터) · 실납 = 월요금 × 0.75
+          <t>※ 유심은 MNP(번호이동) 전용 · 펫네임/기변 없음 · 번이만 입력
+※ 실납 = 월요금 × 0.75 (선택약정 25% 할인 · SK/KT 개통시 · LG 개통 후 고객센터 신청)
+※ 매장·온라인 구조 동일 · 페이백(번이) 값만 다름 · 빈칸(회색)=어드민 등록
 ※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2683,7 +2346,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📡 인터넷+TV 사은품 — 오프라인 · 통신사별 금액 등록</t>
+          <t>📡 인터넷+TV 사은품 — 오프라인 · 통신사별 금액</t>
         </is>
       </c>
     </row>
@@ -2725,14 +2388,14 @@
       <c r="D3" s="19" t="inlineStr"/>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>통신사별 페이백 금액 (만원)</t>
+          <t>통신사별 현금 페이백 (만원)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 사은품 = 현금 페이백 (통신사별 다름) · 결합 요금은 3사 표준 계산기 사용 · 금액 단위: 만원</t>
+          <t>※ 사은품 = 현금 페이백 · 통신사별 다름 · 금액 단위: 만원 · 결합 요금은 3사 표준 계산기 사용</t>
         </is>
       </c>
     </row>

--- a/docs/template-offline-form.xlsx
+++ b/docs/template-offline-form.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -125,12 +125,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00fef3c7"/>
         <bgColor rgb="00fef3c7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f3f4f6"/>
-        <bgColor rgb="00f3f4f6"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -216,7 +210,7 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,16 +219,13 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -602,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -636,7 +627,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>· ② 유심: 통신사 / 요금제(월요금) / 25%↓실납 / 번이 (펫네임/기변 없음)</t>
+          <t>· ② 유심: 통신사 / 요금제(월요금) / 25%↓실납 / 번이</t>
         </is>
       </c>
     </row>
@@ -652,7 +643,7 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>📊 데이터</t>
+          <t>📊 데이터 (샘플 포함)</t>
         </is>
       </c>
     </row>
@@ -660,7 +651,7 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>· 무선: 54행 (3사 × 18종) · 요금제: SK 프리미엄 / KT 초이스스페셜 / LG 프리미어 슈퍼</t>
+          <t>· 무선 54행 (정리3 원본)</t>
         </is>
       </c>
     </row>
@@ -668,7 +659,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· 유심: 9행 (3사 × 3종) · 매장/온라인 구조 동일, 페이백 값만 다름</t>
+          <t>· 유심 9행 (샘플 페이백 포함 · 실제 값으로 덮어쓰기)</t>
         </is>
       </c>
     </row>
@@ -676,7 +667,7 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 인터넷+TV 사은품: 현금만 · 3사별 금액 등록</t>
+          <t>· 인터넷+TV 사은품 1행 (샘플 금액 포함)</t>
         </is>
       </c>
     </row>
@@ -684,7 +675,7 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>📇 유심 요금제 (3사 × 3종)</t>
+          <t>📇 유심 요금제</t>
         </is>
       </c>
     </row>
@@ -764,7 +755,7 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>· 값 단위: 만원 · 음수=페이백(초록) · 양수=부담(빨강) · 빈칸=어드민 등록(회색)</t>
+          <t>· 값 단위: 만원 · 음수=페이백(초록) · 양수=부담(빨강)</t>
         </is>
       </c>
     </row>
@@ -772,7 +763,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· 이 파일은 "오프라인" 전용 · 오프라인: 12개 매장 각자 복사 · 온라인: 통합 1개</t>
+          <t>· 이 파일은 "오프라인" 전용</t>
         </is>
       </c>
     </row>
@@ -780,7 +771,15 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· PK=(통신사+펫네임+요금제 또는 통신사+요금제) · 새 기종은 행 추가</t>
+          <t>· 오프라인: 12개 매장 각자 복사 / 온라인: 통합 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>· PK: 무선=(통신사+펫네임+요금제) · 유심=(통신사+요금제) · 새 기종/요금제는 행 추가</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2087,7 @@
       <c r="A58" s="12" t="inlineStr">
         <is>
           <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
-※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼 (월요금 원 단위)
+※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼 (월요금 원)
 ※ 새 기종은 행 추가 · 컬럼 고정</t>
         </is>
       </c>
@@ -2120,7 +2119,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 — 오프라인 · 9행 (3사 × 3종)</t>
+          <t>📇 유심 시세 — 오프라인 · 9행 (샘플 포함)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2161,9 @@
           <t>24,750</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2180,7 +2181,9 @@
           <t>33,750</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr"/>
+      <c r="D4" s="8" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2198,7 +2201,9 @@
           <t>41,250</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -2216,7 +2221,9 @@
           <t>27,750</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr"/>
+      <c r="D6" s="8" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -2234,7 +2241,9 @@
           <t>37,500</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr"/>
+      <c r="D7" s="8" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -2252,7 +2261,9 @@
           <t>51,750</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr"/>
+      <c r="D8" s="8" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -2270,7 +2281,9 @@
           <t>24,750</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr"/>
+      <c r="D9" s="8" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -2288,7 +2301,9 @@
           <t>45,750</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr"/>
+      <c r="D10" s="8" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -2306,15 +2321,17 @@
           <t>63,750</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr"/>
+      <c r="D11" s="8" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>※ 유심은 MNP(번호이동) 전용 · 펫네임/기변 없음 · 번이만 입력
+          <t>※ 유심은 MNP(번호이동) 전용 · 펫네임/기변 없음 · 번이(만원)만 입력
 ※ 실납 = 월요금 × 0.75 (선택약정 25% 할인 · SK/KT 개통시 · LG 개통 후 고객센터 신청)
-※ 매장·온라인 구조 동일 · 페이백(번이) 값만 다름 · 빈칸(회색)=어드민 등록
-※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</t>
+※ 매장·온라인 구조 동일 · 페이백(번이) 값만 다름 · 샘플 값 입력됨 (실제 정책으로 덮어쓰기)
+※ 유심비: SK/LG 다음 달 청구 · KT 선납(사은품 차감) · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
@@ -2356,17 +2373,17 @@
           <t>종류</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2383,19 +2400,25 @@
           <t>현금</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr"/>
-      <c r="C3" s="18" t="inlineStr"/>
-      <c r="D3" s="19" t="inlineStr"/>
+      <c r="B3" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>55</v>
+      </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>통신사별 현금 페이백 (만원)</t>
+          <t>매장 협상 기준 · 샘플</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 사은품 = 현금 페이백 · 통신사별 다름 · 금액 단위: 만원 · 결합 요금은 3사 표준 계산기 사용</t>
+          <t>※ 현금 페이백 · 통신사별 금액 · 단위: 만원 · 샘플 값 입력됨 (실제 정책으로 덮어쓰기)</t>
         </is>
       </c>
     </row>
